--- a/Bibsam_tidskriftslistor/scifree_data_rsc_fullyoa.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_rsc_fullyoa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_49586995531ED54E2135AA0D205D970814DF8E24" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D67079D-6315-4943-A63D-FA1FF53D6BED}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDCEE98-C1CF-4B33-92C5-53FF593796FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="71">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -221,6 +221,18 @@
   </si>
   <si>
     <t xml:space="preserve">https://doi.org/10.1039/2753-8095/2023 </t>
+  </si>
+  <si>
+    <t>2041-6539</t>
+  </si>
+  <si>
+    <t>2041-6520</t>
+  </si>
+  <si>
+    <t>Chemical Science</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1039/2041-6539/2010</t>
   </si>
 </sst>
 </file>
@@ -276,16 +288,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{025C3C23-87BA-40DE-B00E-4BD58DA68020}" name="Table1" displayName="Table1" ref="A1:G20" totalsRowShown="0">
-  <autoFilter ref="A1:G20" xr:uid="{025C3C23-87BA-40DE-B00E-4BD58DA68020}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD2320CB-C114-4BB0-BE89-E87460834327}" name="Table1" displayName="Table1" ref="A1:G21" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{DD2320CB-C114-4BB0-BE89-E87460834327}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{36AF0596-5827-491E-A84E-1174BC529D41}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{843880D1-5B50-4D89-AFD0-51FD7CE03A2C}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{89EB1EC0-8035-42AB-9E8A-93464DBDB59D}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{39CFED49-193B-4573-9D4D-4AF7504D5F21}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{C1EC44E2-832A-41F4-AA10-1EEA03BE4630}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{0A0A5B99-213E-408A-9550-28A3401E88A3}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{1A8721BE-1586-454F-9667-8A51516CA77E}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{EB719B86-1B33-466C-AEDE-735BF4B3FBE6}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{147058CC-00E3-48C5-8039-0CB61D9618CF}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{115504C7-DB40-4024-BE9C-C168DC4E85DE}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{6F1997FD-C471-4BC0-8D7D-123D210919A8}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{0AF5B36B-7822-4549-B7F2-EFBA1E7FB576}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{D4570A86-85D6-4643-9B69-68A08F17A8E6}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{363A4447-C8D7-4D1E-B524-05414C4D0DDA}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -553,14 +565,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2E9D1D-1E97-4279-B829-8D77F1C9917F}">
-  <dimension ref="A1:G20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF164CB6-C738-4724-85D3-042340F34C64}">
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
@@ -594,13 +606,16 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -614,13 +629,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -634,13 +649,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -654,13 +669,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -674,13 +689,13 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -694,13 +709,13 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -714,13 +729,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -734,13 +749,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -754,13 +769,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -774,13 +789,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
@@ -794,13 +809,13 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -814,13 +829,13 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -834,13 +849,13 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -854,13 +869,13 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -874,13 +889,13 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -894,13 +909,13 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -914,13 +929,13 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
@@ -934,13 +949,13 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -954,18 +969,38 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
         <v>64</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>65</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E21" t="s">
         <v>66</v>
       </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
         <v>8</v>
       </c>
     </row>
